--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.81" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.81" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.81.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0081.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0081.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.81" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.81" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€�ã€‚</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 74</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,14 +672,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: the Court when by any positive rules to refuse the motion to dismiss, onâ€˜</t>
-        </is>
-      </c>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: a</t>
+          <t>L5: isolated marker/symbol line :: ‘</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -723,14 +723,10 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€�ã€‚</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -738,7 +734,11 @@
           <t>L22: isolated marker/symbol line :: 6</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L52: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,17 +772,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: 1850.</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -825,7 +821,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 74</t>
+          <t>L40: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -868,7 +864,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: (</t>
+          <t>L56: isolated marker/symbol line :: 74</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -911,7 +907,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 6</t>
+          <t>L86: isolated marker/symbol line :: (</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -954,7 +950,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L100: symbol-only separator/garbage line :: 411).</t>
+          <t>L93: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -977,12 +973,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -997,7 +993,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: B</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1040,7 +1036,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L123: symbol-only separator/garbage line :: 1850.</t>
+          <t>L100: symbol-only separator/garbage line :: 411).</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1063,12 +1059,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1081,7 +1077,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L101: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1120,7 +1120,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 、。</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1159,7 +1163,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L123: symbol-only separator/garbage line :: 1850.</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
